--- a/artfynd/A 26393-2024 artfynd.xlsx
+++ b/artfynd/A 26393-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118462836</v>
+        <v>118462896</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468973</v>
+        <v>469033</v>
       </c>
       <c r="R2" t="n">
         <v>6429610</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118462896</v>
+        <v>118462649</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469033</v>
+        <v>468855</v>
       </c>
       <c r="R3" t="n">
         <v>6429610</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118529451</v>
+        <v>118462836</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468914</v>
+        <v>468973</v>
       </c>
       <c r="R4" t="n">
         <v>6429610</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blommande och icke blommande</t>
+          <t>Blommande och icke blommande.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118462649</v>
+        <v>118529451</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468855</v>
+        <v>468914</v>
       </c>
       <c r="R5" t="n">
         <v>6429610</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Blommande och icke blommande.</t>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118529601</v>
+        <v>118529200</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>4763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,39 +1167,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468915</v>
+        <v>468855</v>
       </c>
       <c r="R6" t="n">
-        <v>6429721</v>
+        <v>6429610</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,11 +1240,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118529259</v>
+        <v>118529958</v>
       </c>
       <c r="B7" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,36 +1279,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,7 +1319,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468915</v>
+        <v>468916</v>
       </c>
       <c r="R7" t="n">
         <v>6429721</v>
@@ -1360,6 +1355,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118529200</v>
+        <v>118529259</v>
       </c>
       <c r="B8" t="n">
-        <v>4763</v>
+        <v>5166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468855</v>
+        <v>468915</v>
       </c>
       <c r="R8" t="n">
-        <v>6429610</v>
+        <v>6429721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118529653</v>
+        <v>118529601</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468856</v>
+        <v>468915</v>
       </c>
       <c r="R9" t="n">
-        <v>6429722</v>
+        <v>6429721</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118529958</v>
+        <v>118529653</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468916</v>
+        <v>468856</v>
       </c>
       <c r="R10" t="n">
-        <v>6429721</v>
+        <v>6429722</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 26393-2024 artfynd.xlsx
+++ b/artfynd/A 26393-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118462896</v>
+        <v>118462836</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469033</v>
+        <v>468973</v>
       </c>
       <c r="R2" t="n">
         <v>6429610</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118462649</v>
+        <v>118462896</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468855</v>
+        <v>469033</v>
       </c>
       <c r="R3" t="n">
         <v>6429610</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118462836</v>
+        <v>118462649</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468973</v>
+        <v>468855</v>
       </c>
       <c r="R4" t="n">
         <v>6429610</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118529200</v>
+        <v>118529319</v>
       </c>
       <c r="B6" t="n">
         <v>4763</v>
@@ -1194,7 +1194,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468855</v>
+        <v>468914</v>
       </c>
       <c r="R6" t="n">
         <v>6429610</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118529958</v>
+        <v>118529259</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>5166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,39 +1279,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,7 +1316,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468916</v>
+        <v>468915</v>
       </c>
       <c r="R7" t="n">
         <v>6429721</v>
@@ -1355,11 +1352,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118529259</v>
+        <v>118529653</v>
       </c>
       <c r="B8" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,36 +1391,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,13 +1431,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468915</v>
+        <v>468856</v>
       </c>
       <c r="R8" t="n">
-        <v>6429721</v>
+        <v>6429722</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,6 +1467,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,7 +1499,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118529601</v>
+        <v>118529958</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468915</v>
+        <v>468916</v>
       </c>
       <c r="R9" t="n">
         <v>6429721</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118529653</v>
+        <v>118529200</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>4763</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,39 +1631,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,13 +1668,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468856</v>
+        <v>468855</v>
       </c>
       <c r="R10" t="n">
-        <v>6429722</v>
+        <v>6429610</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,11 +1704,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118529319</v>
+        <v>118529601</v>
       </c>
       <c r="B11" t="n">
-        <v>4763</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,36 +1743,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1788,13 +1783,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468914</v>
+        <v>468915</v>
       </c>
       <c r="R11" t="n">
-        <v>6429610</v>
+        <v>6429721</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,6 +1819,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 26393-2024 artfynd.xlsx
+++ b/artfynd/A 26393-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118462836</v>
+        <v>118462896</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468973</v>
+        <v>469033</v>
       </c>
       <c r="R2" t="n">
         <v>6429610</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118462896</v>
+        <v>118462836</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469033</v>
+        <v>468973</v>
       </c>
       <c r="R3" t="n">
         <v>6429610</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118462649</v>
+        <v>118529451</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468855</v>
+        <v>468914</v>
       </c>
       <c r="R4" t="n">
         <v>6429610</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blommande och icke blommande.</t>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118529451</v>
+        <v>118462649</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468914</v>
+        <v>468855</v>
       </c>
       <c r="R5" t="n">
         <v>6429610</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Blommande och icke blommande</t>
+          <t>Blommande och icke blommande.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118529319</v>
+        <v>118529653</v>
       </c>
       <c r="B6" t="n">
-        <v>4763</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,36 +1167,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468914</v>
+        <v>468856</v>
       </c>
       <c r="R6" t="n">
-        <v>6429610</v>
+        <v>6429722</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,6 +1243,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118529259</v>
+        <v>118529200</v>
       </c>
       <c r="B7" t="n">
-        <v>5166</v>
+        <v>4763</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,21 +1291,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,7 +1314,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1316,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468915</v>
+        <v>468855</v>
       </c>
       <c r="R7" t="n">
-        <v>6429721</v>
+        <v>6429610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118529653</v>
+        <v>118529259</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>5166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,39 +1399,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1431,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468856</v>
+        <v>468915</v>
       </c>
       <c r="R8" t="n">
-        <v>6429722</v>
+        <v>6429721</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,11 +1472,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118529958</v>
+        <v>118529601</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468916</v>
+        <v>468915</v>
       </c>
       <c r="R9" t="n">
         <v>6429721</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118529200</v>
+        <v>118529319</v>
       </c>
       <c r="B10" t="n">
         <v>4763</v>
@@ -1658,7 +1658,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468855</v>
+        <v>468914</v>
       </c>
       <c r="R10" t="n">
         <v>6429610</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118529601</v>
+        <v>118529958</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468915</v>
+        <v>468916</v>
       </c>
       <c r="R11" t="n">
         <v>6429721</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 26393-2024 artfynd.xlsx
+++ b/artfynd/A 26393-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118462836</v>
+        <v>118462649</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -830,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468973</v>
+        <v>468855</v>
       </c>
       <c r="R3" t="n">
         <v>6429610</v>
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118529451</v>
+        <v>118462836</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468914</v>
+        <v>468973</v>
       </c>
       <c r="R4" t="n">
         <v>6429610</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blommande och icke blommande</t>
+          <t>Blommande och icke blommande.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118462649</v>
+        <v>118529451</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468855</v>
+        <v>468914</v>
       </c>
       <c r="R5" t="n">
         <v>6429610</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Blommande och icke blommande.</t>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118529653</v>
+        <v>118529319</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>4763</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,39 +1167,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,13 +1204,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468856</v>
+        <v>468914</v>
       </c>
       <c r="R6" t="n">
-        <v>6429722</v>
+        <v>6429610</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,11 +1240,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1619,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118529319</v>
+        <v>118529653</v>
       </c>
       <c r="B10" t="n">
-        <v>4763</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,36 +1623,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,13 +1663,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468914</v>
+        <v>468856</v>
       </c>
       <c r="R10" t="n">
-        <v>6429610</v>
+        <v>6429722</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,6 +1699,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Blommande och icke blommande</t>
         </is>
       </c>
       <c r="AD10" t="b">
